--- a/Documents/caapd-facturacion/escritorio/Base de datos PRUEBA/PADRON_MES_2026-08.xlsx
+++ b/Documents/caapd-facturacion/escritorio/Base de datos PRUEBA/PADRON_MES_2026-08.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14 12:54:39</t>
+          <t>2026-10-15 02:38:02</t>
         </is>
       </c>
     </row>
